--- a/results/Int Task Remove ACC -0.4/Rando_2_permute.xlsx
+++ b/results/Int Task Remove ACC -0.4/Rando_2_permute.xlsx
@@ -440,557 +440,557 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.711450441555086</v>
+        <v>0.7066389782299607</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7066336544406436</v>
+        <v>0.7056201824143171</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7065983399715071</v>
+        <v>0.7032683097536789</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7071598222848142</v>
+        <v>0.703829792066986</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7071598222848142</v>
+        <v>0.7091321087671453</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7083534158497016</v>
+        <v>0.7073770328889507</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7042817817800053</v>
+        <v>0.7132743717751147</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7217354701367362</v>
+        <v>0.7146445376856849</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7242585913537403</v>
+        <v>0.709481704265633</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7227154022903652</v>
+        <v>0.7088142785449161</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7172118463540207</v>
+        <v>0.70972713095315</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7189369315523957</v>
+        <v>0.7036849849975617</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7297358832627872</v>
+        <v>0.7064959457569754</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7280161218537293</v>
+        <v>0.7095187933312086</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7143994659174557</v>
+        <v>0.6925506345601946</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7208900523931853</v>
+        <v>0.6967088689361152</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7153758488782066</v>
+        <v>0.6831555660927149</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7144276820008362</v>
+        <v>0.6722666423428648</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7085039016277308</v>
+        <v>0.6722666423428648</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7060107710905463</v>
+        <v>0.6600128764717615</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6858733605390799</v>
+        <v>0.6676546436574858</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.677518205584868</v>
+        <v>0.6674445314391054</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6582883236523183</v>
+        <v>0.658992306059679</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6575167291206307</v>
+        <v>0.6593351580916984</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6540772063025148</v>
+        <v>0.6593351580916984</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6529171526103248</v>
+        <v>0.6605287516565858</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6457309243304981</v>
+        <v>0.606108799797838</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6402220446048364</v>
+        <v>0.6106908078033975</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.62303685268933</v>
+        <v>0.5961928872755047</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6196679588094871</v>
+        <v>0.5992757162093768</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.62058258581416</v>
+        <v>0.5791276580792761</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.60514892058397</v>
+        <v>0.5890824342636241</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.60514892058397</v>
+        <v>0.5890824342636241</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5975760077400798</v>
+        <v>0.592769158365696</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.59789206336587</v>
+        <v>0.6043098913875995</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6015416984023664</v>
+        <v>0.6000245959066449</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6014710694640932</v>
+        <v>0.6183063109618242</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5878930997301903</v>
+        <v>0.5750634773146239</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5876123585735368</v>
+        <v>0.5742230284411022</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5971504595140019</v>
+        <v>0.5639204313547056</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5921712968253889</v>
+        <v>0.5503635793184272</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6227278954492959</v>
+        <v>0.5556852391197717</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6224118398235057</v>
+        <v>0.5614661644795357</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6100645527200659</v>
+        <v>0.5940532563489738</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5823047180840605</v>
+        <v>0.5644854628608909</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6370756851184473</v>
+        <v>0.5524013484093582</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.631215435297859</v>
+        <v>0.5514884960011244</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.631215435297859</v>
+        <v>0.5442634040592829</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6320576587678196</v>
+        <v>0.5341356047221302</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6199486999661408</v>
+        <v>0.5341356047221302</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6342964896352921</v>
+        <v>0.5234621169799776</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5906898637180918</v>
+        <v>0.5209001321009589</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5884315122897902</v>
+        <v>0.5278797973552835</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5730578284192391</v>
+        <v>0.5279857407626931</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5636043757289155</v>
+        <v>0.5358693854430564</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5467881224130821</v>
+        <v>0.533875981263101</v>
       </c>
     </row>
     <row r="58">
@@ -1000,327 +1000,327 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5228933588212705</v>
+        <v>0.5146460993305513</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5038100585545841</v>
+        <v>0.5097040257075138</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.4935816395993388</v>
+        <v>0.513399622791781</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5084309302221581</v>
+        <v>0.514266513152244</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5043981598144767</v>
+        <v>0.5109311591450988</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5207111375802028</v>
+        <v>0.5086834552954312</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5202502748849884</v>
+        <v>0.5081219729821241</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5023463714116773</v>
+        <v>0.5047177646331448</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.4982800611312981</v>
+        <v>0.505840729259759</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5026430839362821</v>
+        <v>0.5062220900345052</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4967439704536791</v>
+        <v>0.5062220900345052</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.4841599521852736</v>
+        <v>0.5068542012860855</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.4874264518505846</v>
+        <v>0.5038013630320328</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.4921073048777977</v>
+        <v>0.5038013630320328</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.4921073048777977</v>
+        <v>0.5063140141300467</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4912279923422614</v>
+        <v>0.5046631070628229</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.491694178826793</v>
+        <v>0.504980937285052</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4913374849425492</v>
+        <v>0.5012606733102826</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4798164499411189</v>
+        <v>0.4998922819961513</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4798164499411189</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4770443528437198</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5034341990287988</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5051910495034324</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5041227424471401</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5031374865041941</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5152728867928145</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5161151102627751</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5160797957936385</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.512045250789518</v>
+        <v>0.5002807411566536</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5095927585107871</v>
+        <v>0.5002807411566536</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.500054657570322</v>
+        <v>0.5002807411566536</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.500054657570322</v>
+        <v>0.4992972598101466</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4988610640054345</v>
+        <v>0.4998587421234537</v>
       </c>
     </row>
   </sheetData>
